--- a/templates/sitesentry_report_template.xlsx
+++ b/templates/sitesentry_report_template.xlsx
@@ -1,195 +1,198 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Statistics" sheetId="1" ns1:id="R6278ae2995f74285"/>
-    <sheet name="Incidents" sheetId="2" ns1:id="R6df1b60242a04548"/>
-    <sheet name="Error breakdown" sheetId="3" ns1:id="R0c820ad5af294953"/>
+    <sheet name="Statistics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Incidents" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Error breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Statistics'!$A$5:$J$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Statistics'!$A$5:$M$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Statistics'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Statistics'!$A$1:$J$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Incidents'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Statistics'!$A$1:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Incidents'!$A$1:$J$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Incidents'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Incidents'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Error breakdown'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Incidents'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Error breakdown'!$A$1:$G$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Error breakdown'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Error breakdown'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Error breakdown'!$A$1:$G$1</definedName>
   </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
-    <x:numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <x:numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
-  </x:numFmts>
-  <x:fonts count="5">
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF18252C"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="16"/>
-      <x:color rgb="FF18252C"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="10"/>
-      <x:color rgb="FF52616B"/>
-      <x:name val="Arial"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="3">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF18252C"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="3">
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFFFFFFF"/>
-      </x:right>
-    </x:border>
-    <x:border>
-      <x:bottom style="thin">
-        <x:color rgb="FF087D72"/>
-      </x:bottom>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="7">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-  <x:colors>
-    <x:indexedColors>
-      <x:rgbColor rgb="00000000"/>
-      <x:rgbColor rgb="00FFFFFF"/>
-      <x:rgbColor rgb="00FF0000"/>
-      <x:rgbColor rgb="0000FF00"/>
-      <x:rgbColor rgb="000000FF"/>
-      <x:rgbColor rgb="00FFFF00"/>
-      <x:rgbColor rgb="00FF00FF"/>
-      <x:rgbColor rgb="0000FFFF"/>
-      <x:rgbColor rgb="00000000"/>
-      <x:rgbColor rgb="00FFFFFF"/>
-      <x:rgbColor rgb="00FF0000"/>
-      <x:rgbColor rgb="0000FF00"/>
-      <x:rgbColor rgb="000000FF"/>
-      <x:rgbColor rgb="00FFFF00"/>
-      <x:rgbColor rgb="00FF00FF"/>
-      <x:rgbColor rgb="0000FFFF"/>
-      <x:rgbColor rgb="00800000"/>
-      <x:rgbColor rgb="00008000"/>
-      <x:rgbColor rgb="00000080"/>
-      <x:rgbColor rgb="00808000"/>
-      <x:rgbColor rgb="00800080"/>
-      <x:rgbColor rgb="00008080"/>
-      <x:rgbColor rgb="00C0C0C0"/>
-      <x:rgbColor rgb="00808080"/>
-      <x:rgbColor rgb="009999FF"/>
-      <x:rgbColor rgb="00993366"/>
-      <x:rgbColor rgb="00FFFFCC"/>
-      <x:rgbColor rgb="00CCFFFF"/>
-      <x:rgbColor rgb="00660066"/>
-      <x:rgbColor rgb="00FF8080"/>
-      <x:rgbColor rgb="000066CC"/>
-      <x:rgbColor rgb="00CCCCFF"/>
-      <x:rgbColor rgb="00000080"/>
-      <x:rgbColor rgb="00FF00FF"/>
-      <x:rgbColor rgb="00FFFF00"/>
-      <x:rgbColor rgb="0000FFFF"/>
-      <x:rgbColor rgb="00800080"/>
-      <x:rgbColor rgb="00800000"/>
-      <x:rgbColor rgb="00008080"/>
-      <x:rgbColor rgb="000000FF"/>
-      <x:rgbColor rgb="0000CCFF"/>
-      <x:rgbColor rgb="00CCFFFF"/>
-      <x:rgbColor rgb="00CCFFCC"/>
-      <x:rgbColor rgb="00FFFF99"/>
-      <x:rgbColor rgb="0099CCFF"/>
-      <x:rgbColor rgb="00FF99CC"/>
-      <x:rgbColor rgb="00CC99FF"/>
-      <x:rgbColor rgb="00FFCC99"/>
-      <x:rgbColor rgb="003366FF"/>
-      <x:rgbColor rgb="0033CCCC"/>
-      <x:rgbColor rgb="0099CC00"/>
-      <x:rgbColor rgb="00FFCC00"/>
-      <x:rgbColor rgb="00FF9900"/>
-      <x:rgbColor rgb="00FF6600"/>
-      <x:rgbColor rgb="00666699"/>
-      <x:rgbColor rgb="00969696"/>
-      <x:rgbColor rgb="00003366"/>
-      <x:rgbColor rgb="00339966"/>
-      <x:rgbColor rgb="00003300"/>
-      <x:rgbColor rgb="00333300"/>
-      <x:rgbColor rgb="00993300"/>
-      <x:rgbColor rgb="00993366"/>
-      <x:rgbColor rgb="00333399"/>
-      <x:rgbColor rgb="00333333"/>
-    </x:indexedColors>
-  </x:colors>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
+  </numFmts>
+  <fonts count="5">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0018252C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0018252C"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="0052616B"/>
+      <sz val="10"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0018252C"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00FFFFFF"/>
+      </right>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00087D72"/>
+      </bottom>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -356,7 +359,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -365,13 +368,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -405,6 +408,17 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -459,6 +473,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -469,24 +485,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="36" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SiteSentry availability report</t>
+          <t>SiteSentry availability report</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -498,57 +518,59 @@
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">From</t>
+          <t>From</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46323</v>
+        <v>46023</v>
       </c>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">To</t>
+          <t>To</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46323.90175925926</v>
+        <v>46023.99998842592</v>
       </c>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observed through</t>
+          <t>Observed through</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46323.90175925926</v>
+        <v>46023.99998842592</v>
       </c>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOWN checks</t>
+          <t>DOWN checks</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incidents</t>
+          <t>Incidents</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
@@ -556,11 +578,14 @@
       </c>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOWN checks count log observations. Average downtime is per incident. Open incidents are measured through the observation time.</t>
+          <t>DOWN checks count log observations. Average downtime is per incident. Open incidents are measured through the observation time.</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -572,66 +597,85 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitor name</t>
+          <t>Monitor name</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOWN checks</t>
+          <t>DOWN checks</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incidents</t>
+          <t>Incidents</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total DOWN</t>
+          <t>Total DOWN</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Average DOWN</t>
+          <t>Average DOWN</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open incidents</t>
+          <t>Open incidents</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Language</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Web server</t>
+          <t>Web server</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Last status</t>
+          <t>Last status</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current error category</t>
+          <t>Current error category</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Reason code</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>Phase</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
-    <mergeCell ref="A1:J1"/>
+  <autoFilter ref="A5:M5"/>
+  <mergeCells count="5">
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="A1:M1"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A4:M4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -654,61 +698,75 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="48" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitor name</t>
+          <t>Monitor name</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Counted from</t>
+          <t>Counted from</t>
         </is>
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Counted until</t>
+          <t>Counted until</t>
         </is>
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recovered at</t>
+          <t>Recovered at</t>
         </is>
       </c>
       <c r="E1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="F1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carried in</t>
+          <t>Carried in</t>
         </is>
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Still DOWN</t>
+          <t>Still DOWN</t>
         </is>
       </c>
       <c r="H1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error categories</t>
+          <t>Error categories</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>Reason codes</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
@@ -730,37 +788,57 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitor name</t>
+          <t>Monitor name</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error code</t>
+          <t>Error code</t>
         </is>
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error category</t>
+          <t>Error category</t>
         </is>
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOWN checks</t>
+          <t>DOWN checks</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Reason code</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Phase</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
